--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ui_Robot1\Documents\UiPath\Project Cost Data (Dev)\Process 6 - Insert Temporary Transaction Process\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5A5553-00FC-4E55-A364-82652DB0966C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC395B41-03D3-4154-B5F3-D689613540E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="280">
   <si>
     <t>Name</t>
   </si>
@@ -956,6 +956,12 @@
 		@CURRENT_MONTH = N'{CURRENT_MONTH}',
 		@PHASE = N'{PHASE}',
 		@MAIL_ID = @OUTPUT OUTPUT</t>
+  </si>
+  <si>
+    <t>blIncludePreviousMonths</t>
+  </si>
+  <si>
+    <t>BL_INCLUDE_PREVIOUS_MONTHS</t>
   </si>
 </sst>
 </file>
@@ -4853,7 +4859,17 @@
         <v>127</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="32" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A32" s="34" t="s">
+        <v>278</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C32" s="32" t="s">
+        <v>127</v>
+      </c>
+    </row>
     <row r="33" ht="14.25" customHeight="1"/>
     <row r="34" ht="14.25" customHeight="1"/>
     <row r="35" ht="14.25" customHeight="1"/>
@@ -5838,6 +5854,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="82bfd1a8-954c-439e-a286-ef353ebc026f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="5e1c2f93-a2fb-4cf1-9521-08720b4e64d5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005466DA3702E1A14681A7752EFBDA10D8" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a8491fcfc1575a34af03aaf041f1b1c5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="82bfd1a8-954c-439e-a286-ef353ebc026f" xmlns:ns3="5e1c2f93-a2fb-4cf1-9521-08720b4e64d5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7731705f95507e2ea5a143a26fe9bb84" ns2:_="" ns3:_="">
     <xsd:import namespace="82bfd1a8-954c-439e-a286-ef353ebc026f"/>
@@ -6026,17 +6053,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="82bfd1a8-954c-439e-a286-ef353ebc026f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="5e1c2f93-a2fb-4cf1-9521-08720b4e64d5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{596E0A4C-046C-400C-A3F7-F6602DB89E7C}">
   <ds:schemaRefs>
@@ -6046,6 +6062,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7D287A-C322-43DE-86F8-D67EB3F0275B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="82bfd1a8-954c-439e-a286-ef353ebc026f"/>
+    <ds:schemaRef ds:uri="5e1c2f93-a2fb-4cf1-9521-08720b4e64d5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E04EE3E-9070-4F23-8E2B-F6F92BB82ED8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6062,15 +6089,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7D287A-C322-43DE-86F8-D67EB3F0275B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="82bfd1a8-954c-439e-a286-ef353ebc026f"/>
-    <ds:schemaRef ds:uri="5e1c2f93-a2fb-4cf1-9521-08720b4e64d5"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ui_Robot1\Documents\UiPath\Project Cost Data (Dev)\Process 6 - Insert Temporary Transaction Process\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC395B41-03D3-4154-B5F3-D689613540E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F12E5C8-C68E-4C9A-B775-0742080D6790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="286">
   <si>
     <t>Name</t>
   </si>
@@ -443,12 +443,6 @@
   </si>
   <si>
     <t>strSubjectBusinessErrorReport</t>
-  </si>
-  <si>
-    <t>Non Production</t>
-  </si>
-  <si>
-    <t>Non Production/Cost Data Automation</t>
   </si>
   <si>
     <t>STR_SQL_DATABASENAME</t>
@@ -962,6 +956,30 @@
   </si>
   <si>
     <t>BL_INCLUDE_PREVIOUS_MONTHS</t>
+  </si>
+  <si>
+    <t>strPathforConfigfile</t>
+  </si>
+  <si>
+    <t>{MyDocs}\UiPathDocs\Config_Files</t>
+  </si>
+  <si>
+    <t>strProcess3forstart</t>
+  </si>
+  <si>
+    <t>strProcess7forstart</t>
+  </si>
+  <si>
+    <t>Production</t>
+  </si>
+  <si>
+    <t>Production/Cost Data Automation</t>
+  </si>
+  <si>
+    <t>Prod_Process3_TemplatePreparationProcess2</t>
+  </si>
+  <si>
+    <t>Prod_ Process7_Commit_Temp_Table_to_Target_Table_Process</t>
   </si>
 </sst>
 </file>
@@ -1568,7 +1586,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
       <c r="C2" s="3"/>
     </row>
@@ -1577,7 +1595,7 @@
         <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
@@ -1590,47 +1608,47 @@
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1">
       <c r="A5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>126</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="A10" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B10" t="s">
         <v>86</v>
@@ -1641,13 +1659,34 @@
         <v>54</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C11" s="6"/>
     </row>
-    <row r="12" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="13" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="14" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="12" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A13" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="B13" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A14" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="B14" t="s">
+        <v>285</v>
+      </c>
+    </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="17" ht="14.25" customHeight="1"/>
@@ -2634,7 +2673,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Z950"/>
+  <dimension ref="A1:Z949"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
@@ -2728,10 +2767,10 @@
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" s="14" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C7" s="18"/>
     </row>
@@ -2755,10 +2794,10 @@
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="A10" s="14" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C10" s="12"/>
     </row>
@@ -2926,7 +2965,7 @@
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B29" s="16">
         <v>16</v>
@@ -2938,7 +2977,7 @@
         <v>91</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C30" s="12"/>
     </row>
@@ -2947,7 +2986,7 @@
         <v>92</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C31" s="12"/>
     </row>
@@ -2956,7 +2995,7 @@
         <v>93</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C32" s="12"/>
     </row>
@@ -2965,7 +3004,7 @@
         <v>94</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C33" s="12"/>
     </row>
@@ -2974,7 +3013,7 @@
         <v>95</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C34" s="12"/>
     </row>
@@ -2983,7 +3022,7 @@
         <v>96</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C35" s="12"/>
     </row>
@@ -2992,7 +3031,7 @@
         <v>97</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C36" s="12"/>
     </row>
@@ -3001,7 +3040,7 @@
         <v>98</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C37" s="12"/>
     </row>
@@ -3010,7 +3049,7 @@
         <v>99</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C38" s="12"/>
     </row>
@@ -3073,16 +3112,16 @@
         <v>112</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C45" s="12"/>
     </row>
     <row r="46" spans="1:3" ht="14.25" customHeight="1">
       <c r="A46" s="23" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B46" s="23" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C46" s="12"/>
     </row>
@@ -3109,7 +3148,7 @@
         <v>12</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>9</v>
@@ -3120,7 +3159,7 @@
         <v>13</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>10</v>
@@ -3146,10 +3185,10 @@
     </row>
     <row r="53" spans="1:3" ht="30">
       <c r="A53" s="26" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C53" s="12"/>
     </row>
@@ -3173,196 +3212,196 @@
     </row>
     <row r="56" spans="1:3" ht="14.25" customHeight="1">
       <c r="A56" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B56" s="24" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C56" s="12"/>
     </row>
     <row r="57" spans="1:3" ht="14.25" customHeight="1">
       <c r="A57" s="24" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B57" s="24" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C57" s="12"/>
     </row>
     <row r="58" spans="1:3" ht="109.5" customHeight="1">
       <c r="A58" s="12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B58" s="28" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C58" s="12"/>
     </row>
     <row r="59" spans="1:3" ht="14.25" customHeight="1">
       <c r="A59" s="12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B59" s="28" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C59" s="12"/>
     </row>
     <row r="60" spans="1:3" ht="14.25" customHeight="1">
       <c r="A60" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B60" s="28" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C60" s="12"/>
     </row>
     <row r="61" spans="1:3" ht="14.25" customHeight="1">
       <c r="A61" t="s">
+        <v>161</v>
+      </c>
+      <c r="B61" t="s">
+        <v>162</v>
+      </c>
+      <c r="C61" t="s">
         <v>163</v>
-      </c>
-      <c r="B61" t="s">
-        <v>164</v>
-      </c>
-      <c r="C61" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="14.25" customHeight="1">
       <c r="A62" t="s">
+        <v>164</v>
+      </c>
+      <c r="B62" t="s">
+        <v>165</v>
+      </c>
+      <c r="C62" t="s">
         <v>166</v>
-      </c>
-      <c r="B62" t="s">
-        <v>167</v>
-      </c>
-      <c r="C62" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="14.25" customHeight="1">
       <c r="A63" t="s">
+        <v>167</v>
+      </c>
+      <c r="B63" t="s">
+        <v>168</v>
+      </c>
+      <c r="C63" t="s">
         <v>169</v>
-      </c>
-      <c r="B63" t="s">
-        <v>170</v>
-      </c>
-      <c r="C63" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="14.25" customHeight="1">
       <c r="A64" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B64" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="14.25" customHeight="1">
       <c r="A65" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B65" s="29" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="14.25" customHeight="1">
       <c r="A66" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B66" s="29" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="14.25" customHeight="1">
       <c r="A67" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B67">
         <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="14.25" customHeight="1">
       <c r="A68" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B68">
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="14.25" customHeight="1">
       <c r="A69" t="s">
+        <v>179</v>
+      </c>
+      <c r="B69" t="s">
+        <v>180</v>
+      </c>
+      <c r="C69" t="s">
         <v>181</v>
-      </c>
-      <c r="B69" t="s">
-        <v>182</v>
-      </c>
-      <c r="C69" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="14.25" customHeight="1">
       <c r="A70" t="s">
+        <v>182</v>
+      </c>
+      <c r="B70" t="s">
+        <v>183</v>
+      </c>
+      <c r="C70" t="s">
         <v>184</v>
-      </c>
-      <c r="B70" t="s">
-        <v>185</v>
-      </c>
-      <c r="C70" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="14.25" customHeight="1">
       <c r="A71" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B71" t="b">
         <v>1</v>
       </c>
       <c r="C71" s="29" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="14.25" customHeight="1">
       <c r="A72" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B72" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="14.25" customHeight="1">
       <c r="A73" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B73" s="29" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="14.25" customHeight="1">
       <c r="A74" s="24" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B74" s="31" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="14.25" customHeight="1">
       <c r="A75" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="14.25" customHeight="1">
       <c r="A76" s="12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B76" s="12">
         <v>1</v>
@@ -3370,7 +3409,7 @@
     </row>
     <row r="77" spans="1:3" ht="14.25" customHeight="1">
       <c r="A77" s="12" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B77" s="12" t="s">
         <v>44</v>
@@ -3378,7 +3417,7 @@
     </row>
     <row r="78" spans="1:3" ht="14.25" customHeight="1">
       <c r="A78" s="12" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B78" s="12">
         <v>2</v>
@@ -3386,23 +3425,23 @@
     </row>
     <row r="79" spans="1:3" ht="14.25" customHeight="1">
       <c r="A79" s="12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B79" s="28" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="14.25" customHeight="1">
       <c r="A80" s="30" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B80" s="29" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="14.25" customHeight="1">
       <c r="A81" s="24" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B81" s="31" t="s">
         <v>62</v>
@@ -3410,7 +3449,7 @@
     </row>
     <row r="82" spans="1:3" ht="14.25" customHeight="1">
       <c r="A82" s="24" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B82" s="31" t="s">
         <v>72</v>
@@ -3418,50 +3457,50 @@
     </row>
     <row r="83" spans="1:3" ht="14.25" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B83" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="14.25" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B84" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="14.25" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B85" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="14.25" customHeight="1">
       <c r="A86" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B86" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="14.25" customHeight="1">
       <c r="A87" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B87" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="14.25" customHeight="1">
       <c r="A88" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B88" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="14.25" customHeight="1">
@@ -3474,66 +3513,66 @@
     </row>
     <row r="90" spans="1:3" ht="84" customHeight="1">
       <c r="A90" s="36" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B90" s="37" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C90" s="37" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="129" customHeight="1">
       <c r="A91" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B91" s="29" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="132" customHeight="1">
       <c r="A92" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B92" s="29" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="42" customHeight="1">
       <c r="A93" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="29.25" customHeight="1">
       <c r="A94" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B94" s="29" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="27" customHeight="1">
       <c r="A95" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B95" s="29" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="75.75" customHeight="1">
       <c r="A96" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B96" s="29" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="14.25" customHeight="1">
       <c r="A97" s="24" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B97" s="31" t="s">
         <v>64</v>
@@ -3541,73 +3580,73 @@
     </row>
     <row r="98" spans="1:3" ht="14.25" customHeight="1">
       <c r="A98" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B98">
         <v>0</v>
       </c>
       <c r="C98" s="29" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="14.25" customHeight="1">
       <c r="A99" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B99">
         <v>0</v>
       </c>
       <c r="C99" s="29" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="14.25" customHeight="1">
       <c r="A100" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B100">
         <v>1</v>
       </c>
       <c r="C100" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="14.25" customHeight="1">
       <c r="A101" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B101">
         <v>1</v>
       </c>
       <c r="C101" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="14.25" customHeight="1">
       <c r="A102" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B102" t="b">
         <v>1</v>
       </c>
       <c r="C102" s="29" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="14.25" customHeight="1">
       <c r="A103" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B103" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="14.25" customHeight="1">
       <c r="A104" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B104" s="29" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="14.25" customHeight="1"/>
@@ -4455,7 +4494,6 @@
     <row r="947" ht="14.25" customHeight="1"/>
     <row r="948" ht="14.25" customHeight="1"/>
     <row r="949" ht="14.25" customHeight="1"/>
-    <row r="950" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4519,7 +4557,7 @@
         <v>29</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
@@ -4530,7 +4568,7 @@
         <v>30</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
@@ -4541,7 +4579,7 @@
         <v>31</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1">
@@ -4552,7 +4590,7 @@
         <v>32</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1">
@@ -4563,7 +4601,7 @@
         <v>33</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
@@ -4574,7 +4612,7 @@
         <v>34</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
@@ -4585,7 +4623,7 @@
         <v>36</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
       <c r="D8" s="7">
         <v>14</v>
@@ -4599,7 +4637,7 @@
         <v>37</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
       <c r="D9" s="7">
         <v>35</v>
@@ -4613,7 +4651,7 @@
         <v>38</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>42</v>
@@ -4627,7 +4665,7 @@
         <v>39</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>42</v>
@@ -4641,7 +4679,7 @@
         <v>40</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>42</v>
@@ -4655,7 +4693,7 @@
         <v>41</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>42</v>
@@ -4669,7 +4707,7 @@
         <v>123</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
@@ -4680,106 +4718,106 @@
         <v>122</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>126</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>126</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1">
       <c r="A18" s="9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>126</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.25" customHeight="1">
       <c r="A19" s="10" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1">
       <c r="A21" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B21" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>126</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1">
       <c r="A22" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B22" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>126</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1">
       <c r="A24" s="33" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C24" s="32" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="14.25" customHeight="1">
@@ -4787,10 +4825,10 @@
         <v>47</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1">
@@ -4798,76 +4836,76 @@
         <v>48</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C26" s="32" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="14.25" customHeight="1">
       <c r="A27" s="34" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B27" s="35" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C27" s="32" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1">
       <c r="A28" s="34" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C28" s="32" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1">
       <c r="A29" s="34" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C29" s="32" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1">
       <c r="A30" s="34" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C30" s="32" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1">
       <c r="A31" s="34" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C31" s="32" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1">
       <c r="A32" s="34" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C32" s="32" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1"/>
